--- a/data/employees/EMP084/AST-EMP084-06.xlsx
+++ b/data/employees/EMP084/AST-EMP084-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Budget Tracker - Morgan Smith (Finance)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Morgan Smith | Role: Analyst | Location: Hsinchu | Date: 2025-04-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>87</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Cost Centre</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Budget ($K)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Actual ($K)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Variance ($K)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Variance %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>65</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CC-1001 Engineering</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2380</v>
-      </c>
-      <c r="D5" t="n">
-        <v>120</v>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4.8</v>
+        <v>72</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Department KPI performance. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CC-1002 Operations</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-120</v>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>-6.7</v>
+        <v>76</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Section 1: Department KPI performance. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CC-1003 R&amp;D</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3100</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100</v>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3.1</v>
+        <v>72</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Knowledge transfer and onboarding. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CC-1004 IT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1195</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>95</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Section 1: Data quality remediation. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>69</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>64</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>64</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>84</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>84</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>68</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>74</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>82</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>64</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>77</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>96</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>99</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>84</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>98</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>86</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>75</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp084 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>64</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP084</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP084 contributes to ast emp084 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>